--- a/Deliverables/BOM/JLCPCB-BOM.xlsx
+++ b/Deliverables/BOM/JLCPCB-BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ezlo-thermostat\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B20272F-76E9-42E2-95ED-3F984C12EDCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55544E9-5ADB-4580-BB19-CDA5861A064D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="44">
   <si>
     <t>Comment</t>
   </si>
@@ -151,10 +151,7 @@
     <t>C412976</t>
   </si>
   <si>
-    <t>C3606641</t>
-  </si>
-  <si>
-    <t>C1988243</t>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -826,7 +823,7 @@
         <v>31</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/Deliverables/BOM/JLCPCB-BOM.xlsx
+++ b/Deliverables/BOM/JLCPCB-BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ezlo-thermostat\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55544E9-5ADB-4580-BB19-CDA5861A064D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C070EA90-6B4B-4993-A9D1-1054497B796D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
   <si>
     <t>Comment</t>
   </si>
@@ -70,12 +70,6 @@
     <t>C5, C11</t>
   </si>
   <si>
-    <t>C7</t>
-  </si>
-  <si>
-    <t>C12, C14, C15</t>
-  </si>
-  <si>
     <t>C13</t>
   </si>
   <si>
@@ -130,9 +124,6 @@
     <t>C109447</t>
   </si>
   <si>
-    <t>C326057</t>
-  </si>
-  <si>
     <t>C315248</t>
   </si>
   <si>
@@ -152,6 +143,9 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>C7, C12, C14, C15</t>
   </si>
 </sst>
 </file>
@@ -635,7 +629,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -652,10 +646,10 @@
         <v>12</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -666,10 +660,10 @@
         <v>13</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -680,10 +674,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -694,136 +688,122 @@
         <v>15</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="D10" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="7" t="s">
+    <row r="11" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D11" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="6" t="s">
+    <row r="12" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C12" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>43</v>
+      <c r="D12" s="8" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
